--- a/artfynd/A 39091-2022 artfynd.xlsx
+++ b/artfynd/A 39091-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39091-2022 artfynd.xlsx
+++ b/artfynd/A 39091-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2536,6 +2536,123 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123351333</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stigen mellan kraftverket och Krämbols Ö, Krämbol, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>565404</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6539234</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Hanna Stahle</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Hanna Stahle</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39091-2022 artfynd.xlsx
+++ b/artfynd/A 39091-2022 artfynd.xlsx
@@ -2541,7 +2541,7 @@
         <v>123351333</v>
       </c>
       <c r="B17" t="n">
-        <v>100279</v>
+        <v>100451</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 39091-2022 artfynd.xlsx
+++ b/artfynd/A 39091-2022 artfynd.xlsx
@@ -2541,12 +2541,7 @@
         <v>123351333</v>
       </c>
       <c r="B17" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100484</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 39091-2022 artfynd.xlsx
+++ b/artfynd/A 39091-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3381818</v>
+        <v>61693467</v>
       </c>
       <c r="B2" t="n">
-        <v>103177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Värmbol, Underbacken, Srm</t>
+          <t>Krämbol 250 oso, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565466.3869245014</v>
+        <v>565486</v>
       </c>
       <c r="R2" t="n">
-        <v>6539221.710831146</v>
+        <v>6539218</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-09-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,35 +760,35 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>eutrof, gammal granskog</t>
+          <t>Grandominead blandskog, vägkanter</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1744277</v>
+        <v>61693489</v>
       </c>
       <c r="B3" t="n">
-        <v>90673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +796,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>2676</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Värmbol, Underbacken, Srm</t>
+          <t>Krämbol 250 oso, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565330.5030519009</v>
+        <v>565486</v>
       </c>
       <c r="R3" t="n">
-        <v>6539165.27294071</v>
+        <v>6539218</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-09-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,73 +870,83 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>eutrof, gammal granskog</t>
+          <t>Grandominead blandskog, vägkanter</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3477733</v>
+        <v>68116371</v>
       </c>
       <c r="B4" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>3286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Värmbol, Underbacken, Srm</t>
+          <t>Krämbol 145 m oso, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565510.0082879221</v>
+        <v>565410</v>
       </c>
       <c r="R4" t="n">
-        <v>6539177.092879133</v>
+        <v>6539185</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-09-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,76 +984,78 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>eutrof, gammal granskog</t>
+          <t>Grandominerad kalkbarrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Svampinventering 2017 ÅGP Sörmland</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5050342</v>
+        <v>68116256</v>
       </c>
       <c r="B5" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5448</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Värmbol, Underbacken, Srm</t>
+          <t>Krämbol 250 m 0so, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565466.3869245014</v>
+        <v>565477</v>
       </c>
       <c r="R5" t="n">
-        <v>6539221.710831146</v>
+        <v>6539138</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1079,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2009-09-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2009-09-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,60 +1093,60 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>eutrof, gammal granskog</t>
+          <t>Grandominerad kalkbarrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Svampinventering 2017 ÅGP Sörmland</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5280137</v>
+        <v>1744277</v>
       </c>
       <c r="B6" t="n">
-        <v>98430</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565510.0082879221</v>
+        <v>565331</v>
       </c>
       <c r="R6" t="n">
-        <v>6539177.092879133</v>
+        <v>6539165</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,19 +1189,9 @@
           <t>2009-09-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2009-09-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61693070</v>
+        <v>61693262</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,37 +1234,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Krämbol 250 oso, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565486.0655958734</v>
+        <v>565486</v>
       </c>
       <c r="R7" t="n">
-        <v>6539218.437950647</v>
+        <v>6539218</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1336,19 +1304,9 @@
           <t>2016-10-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,37 +1343,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61693167</v>
+        <v>61693334</v>
       </c>
       <c r="B8" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103035</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1431,7 +1384,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1440,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565486.0655958734</v>
+        <v>565486</v>
       </c>
       <c r="R8" t="n">
-        <v>6539218.437950647</v>
+        <v>6539218</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1473,19 +1426,9 @@
           <t>2016-10-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,15 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61693262</v>
+        <v>61693167</v>
       </c>
       <c r="B9" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,35 +1476,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>205976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1575,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565486.0655958734</v>
+        <v>565486</v>
       </c>
       <c r="R9" t="n">
-        <v>6539218.437950647</v>
+        <v>6539218</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1608,19 +1548,9 @@
           <t>2016-10-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,56 +1587,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>61693467</v>
+        <v>3477733</v>
       </c>
       <c r="B10" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2667</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krämbol 250 oso, Srm</t>
+          <t>Värmbol, Underbacken, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565486.0655958734</v>
+        <v>565510</v>
       </c>
       <c r="R10" t="n">
-        <v>6539218.437950647</v>
+        <v>6539177</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1730,22 +1652,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,62 +1669,52 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grandominead blandskog, vägkanter</t>
+          <t>eutrof, gammal granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Håkan Lernefalk</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>61693489</v>
+        <v>61693060</v>
       </c>
       <c r="B11" t="n">
-        <v>92895</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2676</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1825,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565486.0655958734</v>
+        <v>565486</v>
       </c>
       <c r="R11" t="n">
-        <v>6539218.437950647</v>
+        <v>6539218</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -1858,19 +1760,9 @@
           <t>2016-10-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1907,15 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>61693273</v>
+        <v>3381818</v>
       </c>
       <c r="B12" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,16 +1810,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1941,26 +1828,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krämbol 250 oso, Srm</t>
+          <t>Värmbol, Underbacken, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565486.0655958734</v>
+        <v>565466</v>
       </c>
       <c r="R12" t="n">
-        <v>6539218.437950647</v>
+        <v>6539222</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1984,22 +1864,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2011,77 +1881,68 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grandominead blandskog, vägkanter</t>
+          <t>eutrof, gammal granskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Håkan Lernefalk</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>61693360</v>
+        <v>5050342</v>
       </c>
       <c r="B13" t="n">
-        <v>100516</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>225046</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Krämbol 250 oso, Srm</t>
+          <t>Värmbol, Underbacken, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565486.0655958734</v>
+        <v>565466</v>
       </c>
       <c r="R13" t="n">
-        <v>6539218.437950647</v>
+        <v>6539222</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2105,22 +1966,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2132,62 +1983,52 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominead blandskog, vägkanter</t>
+          <t>eutrof, gammal granskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Håkan Lernefalk</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>61693060</v>
+        <v>61693070</v>
       </c>
       <c r="B14" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2200,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565486.0655958734</v>
+        <v>565486</v>
       </c>
       <c r="R14" t="n">
-        <v>6539218.437950647</v>
+        <v>6539218</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2233,19 +2074,9 @@
           <t>2016-10-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2016-10-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2282,55 +2113,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>68116256</v>
+        <v>123351333</v>
       </c>
       <c r="B15" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5448</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krämbol 250 m 0so, Srm</t>
+          <t>Stigen mellan kraftverket och Krämbols Ö, Krämbol, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565476.594679813</v>
+        <v>565404</v>
       </c>
       <c r="R15" t="n">
-        <v>6539137.862382895</v>
+        <v>6539234</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2354,22 +2182,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-10-13</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-10-13</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2382,87 +2210,63 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Grandominerad kalkbarrskog</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hanna Stahle</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Svampinventering 2017 ÅGP Sörmland</t>
-        </is>
-      </c>
+          <t>Hanna Stahle</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68116371</v>
+        <v>5280137</v>
       </c>
       <c r="B16" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3286</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Krämbol 145 m oso, Srm</t>
+          <t>Värmbol, Underbacken, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565410.2057712369</v>
+        <v>565510</v>
       </c>
       <c r="R16" t="n">
-        <v>6539185.18628968</v>
+        <v>6539177</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2486,22 +2290,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-10-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-10-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2510,38 +2304,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grandominerad kalkbarrskog</t>
+          <t>eutrof, gammal granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Svampinventering 2017 ÅGP Sörmland</t>
-        </is>
-      </c>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123351333</v>
+        <v>61693273</v>
       </c>
       <c r="B17" t="n">
-        <v>100484</v>
+        <v>101228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,41 +2338,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stigen mellan kraftverket och Krämbols Ö, Krämbol, Srm</t>
+          <t>Krämbol 250 oso, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565404</v>
+        <v>565486</v>
       </c>
       <c r="R17" t="n">
-        <v>6539234</v>
+        <v>6539218</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2607,22 +2399,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2016-10-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2016-10-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2631,22 +2413,137 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grandominead blandskog, vägkanter</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hanna Stahle</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hanna Stahle</t>
+          <t>Bo Karlsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>61693360</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Krämbol 250 oso, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>565486</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6539218</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2016-10-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2016-10-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Grandominead blandskog, vägkanter</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39091-2022 artfynd.xlsx
+++ b/artfynd/A 39091-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61693467</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61693489</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>Svampinventering 2017 ÅGP Sörmland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68116371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
           <t>Svampinventering 2017 ÅGP Sörmland</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68116256</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1744277</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61693262</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61693334</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61693167</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1686,6 +1731,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3477733</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1796,6 +1846,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61693060</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1898,6 +1953,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3381818</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5050342</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2110,6 +2175,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61693070</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2222,6 +2292,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123351333</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2324,6 +2399,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5280137</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2438,6 +2518,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61693273</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2544,8 +2629,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61693360</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>